--- a/artfynd/A 42021-2026 artfynd.xlsx
+++ b/artfynd/A 42021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137449117</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137449122</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137449118</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137442828</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137449125</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>137442551</v>
       </c>
       <c r="B7" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137442649</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137442579</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>137442591</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137442604</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137442612</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>137442619</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>137442673</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137442687</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>137442694</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137442894</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>137442932</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137449112</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137442936</v>
       </c>
       <c r="B43" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>137442985</v>
       </c>
       <c r="B44" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>137442990</v>
       </c>
       <c r="B45" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137443013</v>
       </c>
       <c r="B46" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137443022</v>
       </c>
       <c r="B47" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>137443079</v>
       </c>
       <c r="B48" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>137443087</v>
       </c>
       <c r="B49" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>137443095</v>
       </c>
       <c r="B50" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>137449113</v>
       </c>
       <c r="B51" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>137449120</v>
       </c>
       <c r="B52" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 42021-2026 artfynd.xlsx
+++ b/artfynd/A 42021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137449117</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137449122</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137449118</v>
       </c>
       <c r="B4" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137442828</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137449125</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>137442551</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137442649</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137442579</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>137442591</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137442604</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137442612</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>137442619</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>137442673</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137442687</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>137442694</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137442894</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>137442932</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137449112</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>137442485</v>
       </c>
       <c r="B20" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137442702</v>
       </c>
       <c r="B21" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>137442816</v>
       </c>
       <c r="B22" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137449107</v>
       </c>
       <c r="B23" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137449109</v>
       </c>
       <c r="B24" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137449110</v>
       </c>
       <c r="B25" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>137449114</v>
       </c>
       <c r="B26" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>137443003</v>
       </c>
       <c r="B27" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137443106</v>
       </c>
       <c r="B28" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>137449123</v>
       </c>
       <c r="B29" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>137442474</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>137442632</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>137442640</v>
       </c>
       <c r="B32" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>137442854</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>137442918</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>137442949</v>
       </c>
       <c r="B35" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>137443011</v>
       </c>
       <c r="B36" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>137449111</v>
       </c>
       <c r="B37" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>137449116</v>
       </c>
       <c r="B38" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>137442881</v>
       </c>
       <c r="B39" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137442936</v>
       </c>
       <c r="B43" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>137442985</v>
       </c>
       <c r="B44" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>137442990</v>
       </c>
       <c r="B45" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137443013</v>
       </c>
       <c r="B46" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137443022</v>
       </c>
       <c r="B47" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>137443079</v>
       </c>
       <c r="B48" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>137443087</v>
       </c>
       <c r="B49" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>137443095</v>
       </c>
       <c r="B50" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>137449113</v>
       </c>
       <c r="B51" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>137449120</v>
       </c>
       <c r="B52" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
